--- a/bankole_sex_specific_splicing_2026/documentation/02_summarized_data_analysis_ujc_documentation_03amm.xlsx
+++ b/bankole_sex_specific_splicing_2026/documentation/02_summarized_data_analysis_ujc_documentation_03amm.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t xml:space="preserve">Process for analyzing data up to creating UJC output files for each dataset
 lists documentation and necessary output</t>
@@ -156,13 +156,23 @@
       <t xml:space="preserve">dorado basecalling
 Demultiplex
 Pychopper to orient reads
-Align reads minimap2</t>
+Align reads minimap2 4 QC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">mclab/lmm_rmg_dros_data/documentation/dorado_basecalling_rmg_lmm.xlsx
+    <t xml:space="preserve">Mel and sim:
+mclab/lmm_rmg_dros_data/documentation/dorado_basecalling_rmg_lmm.xlsx
+Ser:
 mclab/lmm_axk_head_data/documentation/dorado_basecalling_kopp_lmm.xlsx
+Yak and sam:
 mclab/lmm_rlr_head_data/documentation/dorado_basecalling_rlr_lmm.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{PROJ}/dorado_basecalling/pychopper/
+rescue_${SAMPLEID}.fq
+fl_${SAMPLEID}.fq
+unclass_${SAMPLEID}.fq
+Report_${SAMPLEID}.pdf</t>
   </si>
   <si>
     <r>
@@ -173,7 +183,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">
+      <t xml:space="preserve">QC
 </t>
     </r>
     <r>
@@ -190,17 +200,17 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Align qc’d reads to references
-Dorado reads
-Pychopper
-Cat fl+res+unclass
-Minimap2 (nadja)
-Omit unmapped and supplementary 
-Count mapped reads
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location of Aligned Data post-QC for each species</t>
+    <t xml:space="preserve">mclab/lmm_rmg_dros_data/documentation/dorado_basecalling_rmg_lmm.xlsx
+mclab/lmm_axk_head_data/documentation/dorado_basecalling_kopp_lmm.xlsx
+mclab/lmm_rlr_head_data/documentation/dorado_basecalling_rlr_lmm.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Below generates UJC output for each species using fiveSpecies annotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each techRep, convert the aligned reads to GTF via
+SAM → BAM → BED → GTF
+Track the sampleID (sample+techRep) by changing to “source” column in the GTF to be the sampleID</t>
   </si>
   <si>
     <t xml:space="preserve">Location of documentation for each species (1 documentation per dataset)
@@ -213,26 +223,6 @@
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMG (mel/sim)
-PROJ/aln_mel_dorReads_2_dmel6
-PROJ/aln_sim_dorReads_2_dsim2
-RLR (yak/san)
-PROJ/aln_dorReads_2_dyak2_or_dsan1
-KOPP (ser)
-PROJ/aln_ser_dorReads_2_dser1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This folder is referred to as ALN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each techRep, convert the aligned reads to GTF via
-SAM → BAM → BED → GTF
-Track the sampleID (sample+techRep) by changing to “source” column in the GTF to be the sampleID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">see row 22</t>
   </si>
   <si>
     <t xml:space="preserve">ALN/
@@ -522,6 +512,36 @@
 {SPECIES}_data_2_{GENOME}_read_per_jxnHash.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">Sum techReps, normalization, ttests for  UJC and ERP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link UJC to its structural category using sqanti reads ujc_counts.csv file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">see 
+02g_ujc_to_structural_category_02amm.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">documentation for 
+summing techReps
+Flagging UJC on/off at various detection levels
+Normalization
+Ttests
+Create final datasets
+UJC and ERP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_dataPrep_sum_techReps_ujc_erp.xlsx
+For gene normalization and norm ‘fudge factores’ see:
+05_gene_normalization.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UJC:
+PROJ/submission/supplementary/datafiles/datafile_jxnHash_{species}_w_annoFlag_ERP_ESP_info_strCat_flagNovel_02amm.csv
+ERP:
+PROJ/submission/supplementary/datafiles/datafile_erp_{species}_w_annoFlag_flagNovel.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">Complete!</t>
   </si>
 </sst>
@@ -532,7 +552,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -647,8 +667,45 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,12 +740,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF158466"/>
         <bgColor rgb="FF008080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -774,7 +825,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -819,8 +870,24 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -828,6 +895,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1026,11 +1101,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ55"/>
+  <dimension ref="A1:AMJ1048576"/>
   <sheetFormatPr defaultColWidth="7.9765625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="74.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.33"/>
@@ -1178,7 +1253,7 @@
       <c r="AMI13" s="4"/>
       <c r="AMJ13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="1" customFormat="true" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
@@ -1186,6 +1261,9 @@
         <v>13</v>
       </c>
       <c r="C14" s="5"/>
+      <c r="D14" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="AME14" s="3"/>
       <c r="AMF14" s="3"/>
       <c r="AMG14" s="3"/>
@@ -1204,10 +1282,10 @@
     </row>
     <row r="16" s="1" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5"/>
       <c r="AME16" s="3"/>
@@ -1218,6 +1296,7 @@
       <c r="AMJ16" s="4"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
       <c r="C17" s="5"/>
       <c r="AME17" s="3"/>
       <c r="AMF17" s="3"/>
@@ -1226,384 +1305,2395 @@
       <c r="AMI17" s="4"/>
       <c r="AMJ17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="C18" s="5"/>
-      <c r="AME18" s="3"/>
-      <c r="AMF18" s="3"/>
-      <c r="AMG18" s="3"/>
-      <c r="AMH18" s="4"/>
-      <c r="AMI18" s="4"/>
-      <c r="AMJ18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="5"/>
-      <c r="AME19" s="3"/>
-      <c r="AMF19" s="3"/>
-      <c r="AMG19" s="3"/>
-      <c r="AMH19" s="4"/>
-      <c r="AMI19" s="4"/>
-      <c r="AMJ19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="true" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="AME20" s="3"/>
-      <c r="AMF20" s="3"/>
-      <c r="AMG20" s="3"/>
-      <c r="AMH20" s="4"/>
-      <c r="AMI20" s="4"/>
-      <c r="AMJ20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="5"/>
-      <c r="AME21" s="3"/>
-      <c r="AMF21" s="3"/>
-      <c r="AMG21" s="3"/>
-      <c r="AMH21" s="4"/>
-      <c r="AMI21" s="4"/>
-      <c r="AMJ21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="true" ht="249.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="1" t="s">
+    <row r="18" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C18" s="13"/>
+      <c r="AME18" s="14"/>
+      <c r="AMF18" s="14"/>
+      <c r="AMG18" s="14"/>
+      <c r="AMH18" s="15"/>
+      <c r="AMI18" s="15"/>
+      <c r="AMJ18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AME22" s="3"/>
-      <c r="AMF22" s="3"/>
-      <c r="AMG22" s="3"/>
-      <c r="AMH22" s="4"/>
-      <c r="AMI22" s="4"/>
-      <c r="AMJ22" s="4"/>
-    </row>
-    <row r="23" customFormat="false" ht="9.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="106.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="E21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="true" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="AME23" s="3"/>
+      <c r="AMF23" s="3"/>
+      <c r="AMG23" s="3"/>
+      <c r="AMH23" s="4"/>
+      <c r="AMI23" s="4"/>
+      <c r="AMJ23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="AME24" s="3"/>
+      <c r="AMF24" s="3"/>
+      <c r="AMG24" s="3"/>
+      <c r="AMH24" s="4"/>
+      <c r="AMI24" s="4"/>
+      <c r="AMJ24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="true" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="AME28" s="3"/>
-      <c r="AMF28" s="3"/>
-      <c r="AMG28" s="3"/>
-      <c r="AMH28" s="4"/>
-      <c r="AMI28" s="4"/>
-      <c r="AMJ28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="AME29" s="3"/>
-      <c r="AMF29" s="3"/>
-      <c r="AMG29" s="3"/>
-      <c r="AMH29" s="4"/>
-      <c r="AMI29" s="4"/>
-      <c r="AMJ29" s="4"/>
-    </row>
-    <row r="30" customFormat="false" ht="54.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="106.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4"/>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" s="1" customFormat="true" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="1" t="s">
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="AME33" s="3"/>
+      <c r="AMF33" s="3"/>
+      <c r="AMG33" s="3"/>
+      <c r="AMH33" s="4"/>
+      <c r="AMI33" s="4"/>
+      <c r="AMJ33" s="4"/>
+    </row>
+    <row r="34" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="AME34" s="3"/>
+      <c r="AMF34" s="3"/>
+      <c r="AMG34" s="3"/>
+      <c r="AMH34" s="4"/>
+      <c r="AMI34" s="4"/>
+      <c r="AMJ34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
-      <c r="C37" s="12"/>
-    </row>
-    <row r="38" s="1" customFormat="true" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9" t="s">
+      <c r="B35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="AME38" s="3"/>
-      <c r="AMF38" s="3"/>
-      <c r="AMG38" s="3"/>
-      <c r="AMH38" s="4"/>
-      <c r="AMI38" s="4"/>
-      <c r="AMJ38" s="4"/>
-    </row>
-    <row r="39" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="AME39" s="3"/>
-      <c r="AMF39" s="3"/>
-      <c r="AMG39" s="3"/>
-      <c r="AMH39" s="4"/>
-      <c r="AMI39" s="4"/>
-      <c r="AMJ39" s="4"/>
-    </row>
-    <row r="40" customFormat="false" ht="41" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="1" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="119.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="1" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="B39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="119.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" s="1" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="B41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="106.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="E41" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="E43" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="106.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="1" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="B47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="119.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="E47" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" s="1" customFormat="true" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="AME49" s="3"/>
+      <c r="AMF49" s="3"/>
+      <c r="AMG49" s="3"/>
+      <c r="AMH49" s="4"/>
+      <c r="AMI49" s="4"/>
+      <c r="AMJ49" s="4"/>
+    </row>
+    <row r="50" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="AME50" s="3"/>
+      <c r="AMF50" s="3"/>
+      <c r="AMG50" s="3"/>
+      <c r="AMH50" s="4"/>
+      <c r="AMI50" s="4"/>
+      <c r="AMJ50" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="4"/>
-    </row>
-    <row r="54" s="1" customFormat="true" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="9" t="s">
+      <c r="B52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="AME54" s="3"/>
-      <c r="AMF54" s="3"/>
-      <c r="AMG54" s="3"/>
-      <c r="AMH54" s="4"/>
-      <c r="AMI54" s="4"/>
-      <c r="AMJ54" s="4"/>
-    </row>
-    <row r="55" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="AME55" s="3"/>
-      <c r="AMF55" s="3"/>
-      <c r="AMG55" s="3"/>
-      <c r="AMH55" s="4"/>
-      <c r="AMI55" s="4"/>
-      <c r="AMJ55" s="4"/>
-    </row>
+    </row>
+    <row r="54" customFormat="false" ht="119.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+      <c r="AC57" s="1"/>
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AF57" s="1"/>
+      <c r="AG57" s="1"/>
+      <c r="AH57" s="1"/>
+      <c r="AI57" s="1"/>
+      <c r="AJ57" s="1"/>
+      <c r="AK57" s="1"/>
+      <c r="AL57" s="1"/>
+      <c r="AM57" s="1"/>
+      <c r="AN57" s="1"/>
+      <c r="AO57" s="1"/>
+      <c r="AP57" s="1"/>
+      <c r="AQ57" s="1"/>
+      <c r="AR57" s="1"/>
+      <c r="AS57" s="1"/>
+      <c r="AT57" s="1"/>
+      <c r="AU57" s="1"/>
+      <c r="AV57" s="1"/>
+      <c r="AW57" s="1"/>
+      <c r="AX57" s="1"/>
+      <c r="AY57" s="1"/>
+      <c r="AZ57" s="1"/>
+      <c r="BA57" s="1"/>
+      <c r="BB57" s="1"/>
+      <c r="BC57" s="1"/>
+      <c r="BD57" s="1"/>
+      <c r="BE57" s="1"/>
+      <c r="BF57" s="1"/>
+      <c r="BG57" s="1"/>
+      <c r="BH57" s="1"/>
+      <c r="BI57" s="1"/>
+      <c r="BJ57" s="1"/>
+      <c r="BK57" s="1"/>
+      <c r="BL57" s="1"/>
+      <c r="BM57" s="1"/>
+      <c r="BN57" s="1"/>
+      <c r="BO57" s="1"/>
+      <c r="BP57" s="1"/>
+      <c r="BQ57" s="1"/>
+      <c r="BR57" s="1"/>
+      <c r="BS57" s="1"/>
+      <c r="BT57" s="1"/>
+      <c r="BU57" s="1"/>
+      <c r="BV57" s="1"/>
+      <c r="BW57" s="1"/>
+      <c r="BX57" s="1"/>
+      <c r="BY57" s="1"/>
+      <c r="BZ57" s="1"/>
+      <c r="CA57" s="1"/>
+      <c r="CB57" s="1"/>
+      <c r="CC57" s="1"/>
+      <c r="CD57" s="1"/>
+      <c r="CE57" s="1"/>
+      <c r="CF57" s="1"/>
+      <c r="CG57" s="1"/>
+      <c r="CH57" s="1"/>
+      <c r="CI57" s="1"/>
+      <c r="CJ57" s="1"/>
+      <c r="CK57" s="1"/>
+      <c r="CL57" s="1"/>
+      <c r="CM57" s="1"/>
+      <c r="CN57" s="1"/>
+      <c r="CO57" s="1"/>
+      <c r="CP57" s="1"/>
+      <c r="CQ57" s="1"/>
+      <c r="CR57" s="1"/>
+      <c r="CS57" s="1"/>
+      <c r="CT57" s="1"/>
+      <c r="CU57" s="1"/>
+      <c r="CV57" s="1"/>
+      <c r="CW57" s="1"/>
+      <c r="CX57" s="1"/>
+      <c r="CY57" s="1"/>
+      <c r="CZ57" s="1"/>
+      <c r="DA57" s="1"/>
+      <c r="DB57" s="1"/>
+      <c r="DC57" s="1"/>
+      <c r="DD57" s="1"/>
+      <c r="DE57" s="1"/>
+      <c r="DF57" s="1"/>
+      <c r="DG57" s="1"/>
+      <c r="DH57" s="1"/>
+      <c r="DI57" s="1"/>
+      <c r="DJ57" s="1"/>
+      <c r="DK57" s="1"/>
+      <c r="DL57" s="1"/>
+      <c r="DM57" s="1"/>
+      <c r="DN57" s="1"/>
+      <c r="DO57" s="1"/>
+      <c r="DP57" s="1"/>
+      <c r="DQ57" s="1"/>
+      <c r="DR57" s="1"/>
+      <c r="DS57" s="1"/>
+      <c r="DT57" s="1"/>
+      <c r="DU57" s="1"/>
+      <c r="DV57" s="1"/>
+      <c r="DW57" s="1"/>
+      <c r="DX57" s="1"/>
+      <c r="DY57" s="1"/>
+      <c r="DZ57" s="1"/>
+      <c r="EA57" s="1"/>
+      <c r="EB57" s="1"/>
+      <c r="EC57" s="1"/>
+      <c r="ED57" s="1"/>
+      <c r="EE57" s="1"/>
+      <c r="EF57" s="1"/>
+      <c r="EG57" s="1"/>
+      <c r="EH57" s="1"/>
+      <c r="EI57" s="1"/>
+      <c r="EJ57" s="1"/>
+      <c r="EK57" s="1"/>
+      <c r="EL57" s="1"/>
+      <c r="EM57" s="1"/>
+      <c r="EN57" s="1"/>
+      <c r="EO57" s="1"/>
+      <c r="EP57" s="1"/>
+      <c r="EQ57" s="1"/>
+      <c r="ER57" s="1"/>
+      <c r="ES57" s="1"/>
+      <c r="ET57" s="1"/>
+      <c r="EU57" s="1"/>
+      <c r="EV57" s="1"/>
+      <c r="EW57" s="1"/>
+      <c r="EX57" s="1"/>
+      <c r="EY57" s="1"/>
+      <c r="EZ57" s="1"/>
+      <c r="FA57" s="1"/>
+      <c r="FB57" s="1"/>
+      <c r="FC57" s="1"/>
+      <c r="FD57" s="1"/>
+      <c r="FE57" s="1"/>
+      <c r="FF57" s="1"/>
+      <c r="FG57" s="1"/>
+      <c r="FH57" s="1"/>
+      <c r="FI57" s="1"/>
+      <c r="FJ57" s="1"/>
+      <c r="FK57" s="1"/>
+      <c r="FL57" s="1"/>
+      <c r="FM57" s="1"/>
+      <c r="FN57" s="1"/>
+      <c r="FO57" s="1"/>
+      <c r="FP57" s="1"/>
+      <c r="FQ57" s="1"/>
+      <c r="FR57" s="1"/>
+      <c r="FS57" s="1"/>
+      <c r="FT57" s="1"/>
+      <c r="FU57" s="1"/>
+      <c r="FV57" s="1"/>
+      <c r="FW57" s="1"/>
+      <c r="FX57" s="1"/>
+      <c r="FY57" s="1"/>
+      <c r="FZ57" s="1"/>
+      <c r="GA57" s="1"/>
+      <c r="GB57" s="1"/>
+      <c r="GC57" s="1"/>
+      <c r="GD57" s="1"/>
+      <c r="GE57" s="1"/>
+      <c r="GF57" s="1"/>
+      <c r="GG57" s="1"/>
+      <c r="GH57" s="1"/>
+      <c r="GI57" s="1"/>
+      <c r="GJ57" s="1"/>
+      <c r="GK57" s="1"/>
+      <c r="GL57" s="1"/>
+      <c r="GM57" s="1"/>
+      <c r="GN57" s="1"/>
+      <c r="GO57" s="1"/>
+      <c r="GP57" s="1"/>
+      <c r="GQ57" s="1"/>
+      <c r="GR57" s="1"/>
+      <c r="GS57" s="1"/>
+      <c r="GT57" s="1"/>
+      <c r="GU57" s="1"/>
+      <c r="GV57" s="1"/>
+      <c r="GW57" s="1"/>
+      <c r="GX57" s="1"/>
+      <c r="GY57" s="1"/>
+      <c r="GZ57" s="1"/>
+      <c r="HA57" s="1"/>
+      <c r="HB57" s="1"/>
+      <c r="HC57" s="1"/>
+      <c r="HD57" s="1"/>
+      <c r="HE57" s="1"/>
+      <c r="HF57" s="1"/>
+      <c r="HG57" s="1"/>
+      <c r="HH57" s="1"/>
+      <c r="HI57" s="1"/>
+      <c r="HJ57" s="1"/>
+      <c r="HK57" s="1"/>
+      <c r="HL57" s="1"/>
+      <c r="HM57" s="1"/>
+      <c r="HN57" s="1"/>
+      <c r="HO57" s="1"/>
+      <c r="HP57" s="1"/>
+      <c r="HQ57" s="1"/>
+      <c r="HR57" s="1"/>
+      <c r="HS57" s="1"/>
+      <c r="HT57" s="1"/>
+      <c r="HU57" s="1"/>
+      <c r="HV57" s="1"/>
+      <c r="HW57" s="1"/>
+      <c r="HX57" s="1"/>
+      <c r="HY57" s="1"/>
+      <c r="HZ57" s="1"/>
+      <c r="IA57" s="1"/>
+      <c r="IB57" s="1"/>
+      <c r="IC57" s="1"/>
+      <c r="ID57" s="1"/>
+      <c r="IE57" s="1"/>
+      <c r="IF57" s="1"/>
+      <c r="IG57" s="1"/>
+      <c r="IH57" s="1"/>
+      <c r="II57" s="1"/>
+      <c r="IJ57" s="1"/>
+      <c r="IK57" s="1"/>
+      <c r="IL57" s="1"/>
+      <c r="IM57" s="1"/>
+      <c r="IN57" s="1"/>
+      <c r="IO57" s="1"/>
+      <c r="IP57" s="1"/>
+      <c r="IQ57" s="1"/>
+      <c r="IR57" s="1"/>
+      <c r="IS57" s="1"/>
+      <c r="IT57" s="1"/>
+      <c r="IU57" s="1"/>
+      <c r="IV57" s="1"/>
+      <c r="IW57" s="1"/>
+      <c r="IX57" s="1"/>
+      <c r="IY57" s="1"/>
+      <c r="IZ57" s="1"/>
+      <c r="JA57" s="1"/>
+      <c r="JB57" s="1"/>
+      <c r="JC57" s="1"/>
+      <c r="JD57" s="1"/>
+      <c r="JE57" s="1"/>
+      <c r="JF57" s="1"/>
+      <c r="JG57" s="1"/>
+      <c r="JH57" s="1"/>
+      <c r="JI57" s="1"/>
+      <c r="JJ57" s="1"/>
+      <c r="JK57" s="1"/>
+      <c r="JL57" s="1"/>
+      <c r="JM57" s="1"/>
+      <c r="JN57" s="1"/>
+      <c r="JO57" s="1"/>
+      <c r="JP57" s="1"/>
+      <c r="JQ57" s="1"/>
+      <c r="JR57" s="1"/>
+      <c r="JS57" s="1"/>
+      <c r="JT57" s="1"/>
+      <c r="JU57" s="1"/>
+      <c r="JV57" s="1"/>
+      <c r="JW57" s="1"/>
+      <c r="JX57" s="1"/>
+      <c r="JY57" s="1"/>
+      <c r="JZ57" s="1"/>
+      <c r="KA57" s="1"/>
+      <c r="KB57" s="1"/>
+      <c r="KC57" s="1"/>
+      <c r="KD57" s="1"/>
+      <c r="KE57" s="1"/>
+      <c r="KF57" s="1"/>
+      <c r="KG57" s="1"/>
+      <c r="KH57" s="1"/>
+      <c r="KI57" s="1"/>
+      <c r="KJ57" s="1"/>
+      <c r="KK57" s="1"/>
+      <c r="KL57" s="1"/>
+      <c r="KM57" s="1"/>
+      <c r="KN57" s="1"/>
+      <c r="KO57" s="1"/>
+      <c r="KP57" s="1"/>
+      <c r="KQ57" s="1"/>
+      <c r="KR57" s="1"/>
+      <c r="KS57" s="1"/>
+      <c r="KT57" s="1"/>
+      <c r="KU57" s="1"/>
+      <c r="KV57" s="1"/>
+      <c r="KW57" s="1"/>
+      <c r="KX57" s="1"/>
+      <c r="KY57" s="1"/>
+      <c r="KZ57" s="1"/>
+      <c r="LA57" s="1"/>
+      <c r="LB57" s="1"/>
+      <c r="LC57" s="1"/>
+      <c r="LD57" s="1"/>
+      <c r="LE57" s="1"/>
+      <c r="LF57" s="1"/>
+      <c r="LG57" s="1"/>
+      <c r="LH57" s="1"/>
+      <c r="LI57" s="1"/>
+      <c r="LJ57" s="1"/>
+      <c r="LK57" s="1"/>
+      <c r="LL57" s="1"/>
+      <c r="LM57" s="1"/>
+      <c r="LN57" s="1"/>
+      <c r="LO57" s="1"/>
+      <c r="LP57" s="1"/>
+      <c r="LQ57" s="1"/>
+      <c r="LR57" s="1"/>
+      <c r="LS57" s="1"/>
+      <c r="LT57" s="1"/>
+      <c r="LU57" s="1"/>
+      <c r="LV57" s="1"/>
+      <c r="LW57" s="1"/>
+      <c r="LX57" s="1"/>
+      <c r="LY57" s="1"/>
+      <c r="LZ57" s="1"/>
+      <c r="MA57" s="1"/>
+      <c r="MB57" s="1"/>
+      <c r="MC57" s="1"/>
+      <c r="MD57" s="1"/>
+      <c r="ME57" s="1"/>
+      <c r="MF57" s="1"/>
+      <c r="MG57" s="1"/>
+      <c r="MH57" s="1"/>
+      <c r="MI57" s="1"/>
+      <c r="MJ57" s="1"/>
+      <c r="MK57" s="1"/>
+      <c r="ML57" s="1"/>
+      <c r="MM57" s="1"/>
+      <c r="MN57" s="1"/>
+      <c r="MO57" s="1"/>
+      <c r="MP57" s="1"/>
+      <c r="MQ57" s="1"/>
+      <c r="MR57" s="1"/>
+      <c r="MS57" s="1"/>
+      <c r="MT57" s="1"/>
+      <c r="MU57" s="1"/>
+      <c r="MV57" s="1"/>
+      <c r="MW57" s="1"/>
+      <c r="MX57" s="1"/>
+      <c r="MY57" s="1"/>
+      <c r="MZ57" s="1"/>
+      <c r="NA57" s="1"/>
+      <c r="NB57" s="1"/>
+      <c r="NC57" s="1"/>
+      <c r="ND57" s="1"/>
+      <c r="NE57" s="1"/>
+      <c r="NF57" s="1"/>
+      <c r="NG57" s="1"/>
+      <c r="NH57" s="1"/>
+      <c r="NI57" s="1"/>
+      <c r="NJ57" s="1"/>
+      <c r="NK57" s="1"/>
+      <c r="NL57" s="1"/>
+      <c r="NM57" s="1"/>
+      <c r="NN57" s="1"/>
+      <c r="NO57" s="1"/>
+      <c r="NP57" s="1"/>
+      <c r="NQ57" s="1"/>
+      <c r="NR57" s="1"/>
+      <c r="NS57" s="1"/>
+      <c r="NT57" s="1"/>
+      <c r="NU57" s="1"/>
+      <c r="NV57" s="1"/>
+      <c r="NW57" s="1"/>
+      <c r="NX57" s="1"/>
+      <c r="NY57" s="1"/>
+      <c r="NZ57" s="1"/>
+      <c r="OA57" s="1"/>
+      <c r="OB57" s="1"/>
+      <c r="OC57" s="1"/>
+      <c r="OD57" s="1"/>
+      <c r="OE57" s="1"/>
+      <c r="OF57" s="1"/>
+      <c r="OG57" s="1"/>
+      <c r="OH57" s="1"/>
+      <c r="OI57" s="1"/>
+      <c r="OJ57" s="1"/>
+      <c r="OK57" s="1"/>
+      <c r="OL57" s="1"/>
+      <c r="OM57" s="1"/>
+      <c r="ON57" s="1"/>
+      <c r="OO57" s="1"/>
+      <c r="OP57" s="1"/>
+      <c r="OQ57" s="1"/>
+      <c r="OR57" s="1"/>
+      <c r="OS57" s="1"/>
+      <c r="OT57" s="1"/>
+      <c r="OU57" s="1"/>
+      <c r="OV57" s="1"/>
+      <c r="OW57" s="1"/>
+      <c r="OX57" s="1"/>
+      <c r="OY57" s="1"/>
+      <c r="OZ57" s="1"/>
+      <c r="PA57" s="1"/>
+      <c r="PB57" s="1"/>
+      <c r="PC57" s="1"/>
+      <c r="PD57" s="1"/>
+      <c r="PE57" s="1"/>
+      <c r="PF57" s="1"/>
+      <c r="PG57" s="1"/>
+      <c r="PH57" s="1"/>
+      <c r="PI57" s="1"/>
+      <c r="PJ57" s="1"/>
+      <c r="PK57" s="1"/>
+      <c r="PL57" s="1"/>
+      <c r="PM57" s="1"/>
+      <c r="PN57" s="1"/>
+      <c r="PO57" s="1"/>
+      <c r="PP57" s="1"/>
+      <c r="PQ57" s="1"/>
+      <c r="PR57" s="1"/>
+      <c r="PS57" s="1"/>
+      <c r="PT57" s="1"/>
+      <c r="PU57" s="1"/>
+      <c r="PV57" s="1"/>
+      <c r="PW57" s="1"/>
+      <c r="PX57" s="1"/>
+      <c r="PY57" s="1"/>
+      <c r="PZ57" s="1"/>
+      <c r="QA57" s="1"/>
+      <c r="QB57" s="1"/>
+      <c r="QC57" s="1"/>
+      <c r="QD57" s="1"/>
+      <c r="QE57" s="1"/>
+      <c r="QF57" s="1"/>
+      <c r="QG57" s="1"/>
+      <c r="QH57" s="1"/>
+      <c r="QI57" s="1"/>
+      <c r="QJ57" s="1"/>
+      <c r="QK57" s="1"/>
+      <c r="QL57" s="1"/>
+      <c r="QM57" s="1"/>
+      <c r="QN57" s="1"/>
+      <c r="QO57" s="1"/>
+      <c r="QP57" s="1"/>
+      <c r="QQ57" s="1"/>
+      <c r="QR57" s="1"/>
+      <c r="QS57" s="1"/>
+      <c r="QT57" s="1"/>
+      <c r="QU57" s="1"/>
+      <c r="QV57" s="1"/>
+      <c r="QW57" s="1"/>
+      <c r="QX57" s="1"/>
+      <c r="QY57" s="1"/>
+      <c r="QZ57" s="1"/>
+      <c r="RA57" s="1"/>
+      <c r="RB57" s="1"/>
+      <c r="RC57" s="1"/>
+      <c r="RD57" s="1"/>
+      <c r="RE57" s="1"/>
+      <c r="RF57" s="1"/>
+      <c r="RG57" s="1"/>
+      <c r="RH57" s="1"/>
+      <c r="RI57" s="1"/>
+      <c r="RJ57" s="1"/>
+      <c r="RK57" s="1"/>
+      <c r="RL57" s="1"/>
+      <c r="RM57" s="1"/>
+      <c r="RN57" s="1"/>
+      <c r="RO57" s="1"/>
+      <c r="RP57" s="1"/>
+      <c r="RQ57" s="1"/>
+      <c r="RR57" s="1"/>
+      <c r="RS57" s="1"/>
+      <c r="RT57" s="1"/>
+      <c r="RU57" s="1"/>
+      <c r="RV57" s="1"/>
+      <c r="RW57" s="1"/>
+      <c r="RX57" s="1"/>
+      <c r="RY57" s="1"/>
+      <c r="RZ57" s="1"/>
+      <c r="SA57" s="1"/>
+      <c r="SB57" s="1"/>
+      <c r="SC57" s="1"/>
+      <c r="SD57" s="1"/>
+      <c r="SE57" s="1"/>
+      <c r="SF57" s="1"/>
+      <c r="SG57" s="1"/>
+      <c r="SH57" s="1"/>
+      <c r="SI57" s="1"/>
+      <c r="SJ57" s="1"/>
+      <c r="SK57" s="1"/>
+      <c r="SL57" s="1"/>
+      <c r="SM57" s="1"/>
+      <c r="SN57" s="1"/>
+      <c r="SO57" s="1"/>
+      <c r="SP57" s="1"/>
+      <c r="SQ57" s="1"/>
+      <c r="SR57" s="1"/>
+      <c r="SS57" s="1"/>
+      <c r="ST57" s="1"/>
+      <c r="SU57" s="1"/>
+      <c r="SV57" s="1"/>
+      <c r="SW57" s="1"/>
+      <c r="SX57" s="1"/>
+      <c r="SY57" s="1"/>
+      <c r="SZ57" s="1"/>
+      <c r="TA57" s="1"/>
+      <c r="TB57" s="1"/>
+      <c r="TC57" s="1"/>
+      <c r="TD57" s="1"/>
+      <c r="TE57" s="1"/>
+      <c r="TF57" s="1"/>
+      <c r="TG57" s="1"/>
+      <c r="TH57" s="1"/>
+      <c r="TI57" s="1"/>
+      <c r="TJ57" s="1"/>
+      <c r="TK57" s="1"/>
+      <c r="TL57" s="1"/>
+      <c r="TM57" s="1"/>
+      <c r="TN57" s="1"/>
+      <c r="TO57" s="1"/>
+      <c r="TP57" s="1"/>
+      <c r="TQ57" s="1"/>
+      <c r="TR57" s="1"/>
+      <c r="TS57" s="1"/>
+      <c r="TT57" s="1"/>
+      <c r="TU57" s="1"/>
+      <c r="TV57" s="1"/>
+      <c r="TW57" s="1"/>
+      <c r="TX57" s="1"/>
+      <c r="TY57" s="1"/>
+      <c r="TZ57" s="1"/>
+      <c r="UA57" s="1"/>
+      <c r="UB57" s="1"/>
+      <c r="UC57" s="1"/>
+      <c r="UD57" s="1"/>
+      <c r="UE57" s="1"/>
+      <c r="UF57" s="1"/>
+      <c r="UG57" s="1"/>
+      <c r="UH57" s="1"/>
+      <c r="UI57" s="1"/>
+      <c r="UJ57" s="1"/>
+      <c r="UK57" s="1"/>
+      <c r="UL57" s="1"/>
+      <c r="UM57" s="1"/>
+      <c r="UN57" s="1"/>
+      <c r="UO57" s="1"/>
+      <c r="UP57" s="1"/>
+      <c r="UQ57" s="1"/>
+      <c r="UR57" s="1"/>
+      <c r="US57" s="1"/>
+      <c r="UT57" s="1"/>
+      <c r="UU57" s="1"/>
+      <c r="UV57" s="1"/>
+      <c r="UW57" s="1"/>
+      <c r="UX57" s="1"/>
+      <c r="UY57" s="1"/>
+      <c r="UZ57" s="1"/>
+      <c r="VA57" s="1"/>
+      <c r="VB57" s="1"/>
+      <c r="VC57" s="1"/>
+      <c r="VD57" s="1"/>
+      <c r="VE57" s="1"/>
+      <c r="VF57" s="1"/>
+      <c r="VG57" s="1"/>
+      <c r="VH57" s="1"/>
+      <c r="VI57" s="1"/>
+      <c r="VJ57" s="1"/>
+      <c r="VK57" s="1"/>
+      <c r="VL57" s="1"/>
+      <c r="VM57" s="1"/>
+      <c r="VN57" s="1"/>
+      <c r="VO57" s="1"/>
+      <c r="VP57" s="1"/>
+      <c r="VQ57" s="1"/>
+      <c r="VR57" s="1"/>
+      <c r="VS57" s="1"/>
+      <c r="VT57" s="1"/>
+      <c r="VU57" s="1"/>
+      <c r="VV57" s="1"/>
+      <c r="VW57" s="1"/>
+      <c r="VX57" s="1"/>
+      <c r="VY57" s="1"/>
+      <c r="VZ57" s="1"/>
+      <c r="WA57" s="1"/>
+      <c r="WB57" s="1"/>
+      <c r="WC57" s="1"/>
+      <c r="WD57" s="1"/>
+      <c r="WE57" s="1"/>
+      <c r="WF57" s="1"/>
+      <c r="WG57" s="1"/>
+      <c r="WH57" s="1"/>
+      <c r="WI57" s="1"/>
+      <c r="WJ57" s="1"/>
+      <c r="WK57" s="1"/>
+      <c r="WL57" s="1"/>
+      <c r="WM57" s="1"/>
+      <c r="WN57" s="1"/>
+      <c r="WO57" s="1"/>
+      <c r="WP57" s="1"/>
+      <c r="WQ57" s="1"/>
+      <c r="WR57" s="1"/>
+      <c r="WS57" s="1"/>
+      <c r="WT57" s="1"/>
+      <c r="WU57" s="1"/>
+      <c r="WV57" s="1"/>
+      <c r="WW57" s="1"/>
+      <c r="WX57" s="1"/>
+      <c r="WY57" s="1"/>
+      <c r="WZ57" s="1"/>
+      <c r="XA57" s="1"/>
+      <c r="XB57" s="1"/>
+      <c r="XC57" s="1"/>
+      <c r="XD57" s="1"/>
+      <c r="XE57" s="1"/>
+      <c r="XF57" s="1"/>
+      <c r="XG57" s="1"/>
+      <c r="XH57" s="1"/>
+      <c r="XI57" s="1"/>
+      <c r="XJ57" s="1"/>
+      <c r="XK57" s="1"/>
+      <c r="XL57" s="1"/>
+      <c r="XM57" s="1"/>
+      <c r="XN57" s="1"/>
+      <c r="XO57" s="1"/>
+      <c r="XP57" s="1"/>
+      <c r="XQ57" s="1"/>
+      <c r="XR57" s="1"/>
+      <c r="XS57" s="1"/>
+      <c r="XT57" s="1"/>
+      <c r="XU57" s="1"/>
+      <c r="XV57" s="1"/>
+      <c r="XW57" s="1"/>
+      <c r="XX57" s="1"/>
+      <c r="XY57" s="1"/>
+      <c r="XZ57" s="1"/>
+      <c r="YA57" s="1"/>
+      <c r="YB57" s="1"/>
+      <c r="YC57" s="1"/>
+      <c r="YD57" s="1"/>
+      <c r="YE57" s="1"/>
+      <c r="YF57" s="1"/>
+      <c r="YG57" s="1"/>
+      <c r="YH57" s="1"/>
+      <c r="YI57" s="1"/>
+      <c r="YJ57" s="1"/>
+      <c r="YK57" s="1"/>
+      <c r="YL57" s="1"/>
+      <c r="YM57" s="1"/>
+      <c r="YN57" s="1"/>
+      <c r="YO57" s="1"/>
+      <c r="YP57" s="1"/>
+      <c r="YQ57" s="1"/>
+      <c r="YR57" s="1"/>
+      <c r="YS57" s="1"/>
+      <c r="YT57" s="1"/>
+      <c r="YU57" s="1"/>
+      <c r="YV57" s="1"/>
+      <c r="YW57" s="1"/>
+      <c r="YX57" s="1"/>
+      <c r="YY57" s="1"/>
+      <c r="YZ57" s="1"/>
+      <c r="ZA57" s="1"/>
+      <c r="ZB57" s="1"/>
+      <c r="ZC57" s="1"/>
+      <c r="ZD57" s="1"/>
+      <c r="ZE57" s="1"/>
+      <c r="ZF57" s="1"/>
+      <c r="ZG57" s="1"/>
+      <c r="ZH57" s="1"/>
+      <c r="ZI57" s="1"/>
+      <c r="ZJ57" s="1"/>
+      <c r="ZK57" s="1"/>
+      <c r="ZL57" s="1"/>
+      <c r="ZM57" s="1"/>
+      <c r="ZN57" s="1"/>
+      <c r="ZO57" s="1"/>
+      <c r="ZP57" s="1"/>
+      <c r="ZQ57" s="1"/>
+      <c r="ZR57" s="1"/>
+      <c r="ZS57" s="1"/>
+      <c r="ZT57" s="1"/>
+      <c r="ZU57" s="1"/>
+      <c r="ZV57" s="1"/>
+      <c r="ZW57" s="1"/>
+      <c r="ZX57" s="1"/>
+      <c r="ZY57" s="1"/>
+      <c r="ZZ57" s="1"/>
+      <c r="AAA57" s="1"/>
+      <c r="AAB57" s="1"/>
+      <c r="AAC57" s="1"/>
+      <c r="AAD57" s="1"/>
+      <c r="AAE57" s="1"/>
+      <c r="AAF57" s="1"/>
+      <c r="AAG57" s="1"/>
+      <c r="AAH57" s="1"/>
+      <c r="AAI57" s="1"/>
+      <c r="AAJ57" s="1"/>
+      <c r="AAK57" s="1"/>
+      <c r="AAL57" s="1"/>
+      <c r="AAM57" s="1"/>
+      <c r="AAN57" s="1"/>
+      <c r="AAO57" s="1"/>
+      <c r="AAP57" s="1"/>
+      <c r="AAQ57" s="1"/>
+      <c r="AAR57" s="1"/>
+      <c r="AAS57" s="1"/>
+      <c r="AAT57" s="1"/>
+      <c r="AAU57" s="1"/>
+      <c r="AAV57" s="1"/>
+      <c r="AAW57" s="1"/>
+      <c r="AAX57" s="1"/>
+      <c r="AAY57" s="1"/>
+      <c r="AAZ57" s="1"/>
+      <c r="ABA57" s="1"/>
+      <c r="ABB57" s="1"/>
+      <c r="ABC57" s="1"/>
+      <c r="ABD57" s="1"/>
+      <c r="ABE57" s="1"/>
+      <c r="ABF57" s="1"/>
+      <c r="ABG57" s="1"/>
+      <c r="ABH57" s="1"/>
+      <c r="ABI57" s="1"/>
+      <c r="ABJ57" s="1"/>
+      <c r="ABK57" s="1"/>
+      <c r="ABL57" s="1"/>
+      <c r="ABM57" s="1"/>
+      <c r="ABN57" s="1"/>
+      <c r="ABO57" s="1"/>
+      <c r="ABP57" s="1"/>
+      <c r="ABQ57" s="1"/>
+      <c r="ABR57" s="1"/>
+      <c r="ABS57" s="1"/>
+      <c r="ABT57" s="1"/>
+      <c r="ABU57" s="1"/>
+      <c r="ABV57" s="1"/>
+      <c r="ABW57" s="1"/>
+      <c r="ABX57" s="1"/>
+      <c r="ABY57" s="1"/>
+      <c r="ABZ57" s="1"/>
+      <c r="ACA57" s="1"/>
+      <c r="ACB57" s="1"/>
+      <c r="ACC57" s="1"/>
+      <c r="ACD57" s="1"/>
+      <c r="ACE57" s="1"/>
+      <c r="ACF57" s="1"/>
+      <c r="ACG57" s="1"/>
+      <c r="ACH57" s="1"/>
+      <c r="ACI57" s="1"/>
+      <c r="ACJ57" s="1"/>
+      <c r="ACK57" s="1"/>
+      <c r="ACL57" s="1"/>
+      <c r="ACM57" s="1"/>
+      <c r="ACN57" s="1"/>
+      <c r="ACO57" s="1"/>
+      <c r="ACP57" s="1"/>
+      <c r="ACQ57" s="1"/>
+      <c r="ACR57" s="1"/>
+      <c r="ACS57" s="1"/>
+      <c r="ACT57" s="1"/>
+      <c r="ACU57" s="1"/>
+      <c r="ACV57" s="1"/>
+      <c r="ACW57" s="1"/>
+      <c r="ACX57" s="1"/>
+      <c r="ACY57" s="1"/>
+      <c r="ACZ57" s="1"/>
+      <c r="ADA57" s="1"/>
+      <c r="ADB57" s="1"/>
+      <c r="ADC57" s="1"/>
+      <c r="ADD57" s="1"/>
+      <c r="ADE57" s="1"/>
+      <c r="ADF57" s="1"/>
+      <c r="ADG57" s="1"/>
+      <c r="ADH57" s="1"/>
+      <c r="ADI57" s="1"/>
+      <c r="ADJ57" s="1"/>
+      <c r="ADK57" s="1"/>
+      <c r="ADL57" s="1"/>
+      <c r="ADM57" s="1"/>
+      <c r="ADN57" s="1"/>
+      <c r="ADO57" s="1"/>
+      <c r="ADP57" s="1"/>
+      <c r="ADQ57" s="1"/>
+      <c r="ADR57" s="1"/>
+      <c r="ADS57" s="1"/>
+      <c r="ADT57" s="1"/>
+      <c r="ADU57" s="1"/>
+      <c r="ADV57" s="1"/>
+      <c r="ADW57" s="1"/>
+      <c r="ADX57" s="1"/>
+      <c r="ADY57" s="1"/>
+      <c r="ADZ57" s="1"/>
+      <c r="AEA57" s="1"/>
+      <c r="AEB57" s="1"/>
+      <c r="AEC57" s="1"/>
+      <c r="AED57" s="1"/>
+      <c r="AEE57" s="1"/>
+      <c r="AEF57" s="1"/>
+      <c r="AEG57" s="1"/>
+      <c r="AEH57" s="1"/>
+      <c r="AEI57" s="1"/>
+      <c r="AEJ57" s="1"/>
+      <c r="AEK57" s="1"/>
+      <c r="AEL57" s="1"/>
+      <c r="AEM57" s="1"/>
+      <c r="AEN57" s="1"/>
+      <c r="AEO57" s="1"/>
+      <c r="AEP57" s="1"/>
+      <c r="AEQ57" s="1"/>
+      <c r="AER57" s="1"/>
+      <c r="AES57" s="1"/>
+      <c r="AET57" s="1"/>
+      <c r="AEU57" s="1"/>
+      <c r="AEV57" s="1"/>
+      <c r="AEW57" s="1"/>
+      <c r="AEX57" s="1"/>
+      <c r="AEY57" s="1"/>
+      <c r="AEZ57" s="1"/>
+      <c r="AFA57" s="1"/>
+      <c r="AFB57" s="1"/>
+      <c r="AFC57" s="1"/>
+      <c r="AFD57" s="1"/>
+      <c r="AFE57" s="1"/>
+      <c r="AFF57" s="1"/>
+      <c r="AFG57" s="1"/>
+      <c r="AFH57" s="1"/>
+      <c r="AFI57" s="1"/>
+      <c r="AFJ57" s="1"/>
+      <c r="AFK57" s="1"/>
+      <c r="AFL57" s="1"/>
+      <c r="AFM57" s="1"/>
+      <c r="AFN57" s="1"/>
+      <c r="AFO57" s="1"/>
+      <c r="AFP57" s="1"/>
+      <c r="AFQ57" s="1"/>
+      <c r="AFR57" s="1"/>
+      <c r="AFS57" s="1"/>
+      <c r="AFT57" s="1"/>
+      <c r="AFU57" s="1"/>
+      <c r="AFV57" s="1"/>
+      <c r="AFW57" s="1"/>
+      <c r="AFX57" s="1"/>
+      <c r="AFY57" s="1"/>
+      <c r="AFZ57" s="1"/>
+      <c r="AGA57" s="1"/>
+      <c r="AGB57" s="1"/>
+      <c r="AGC57" s="1"/>
+      <c r="AGD57" s="1"/>
+      <c r="AGE57" s="1"/>
+      <c r="AGF57" s="1"/>
+      <c r="AGG57" s="1"/>
+      <c r="AGH57" s="1"/>
+      <c r="AGI57" s="1"/>
+      <c r="AGJ57" s="1"/>
+      <c r="AGK57" s="1"/>
+      <c r="AGL57" s="1"/>
+      <c r="AGM57" s="1"/>
+      <c r="AGN57" s="1"/>
+      <c r="AGO57" s="1"/>
+      <c r="AGP57" s="1"/>
+      <c r="AGQ57" s="1"/>
+      <c r="AGR57" s="1"/>
+      <c r="AGS57" s="1"/>
+      <c r="AGT57" s="1"/>
+      <c r="AGU57" s="1"/>
+      <c r="AGV57" s="1"/>
+      <c r="AGW57" s="1"/>
+      <c r="AGX57" s="1"/>
+      <c r="AGY57" s="1"/>
+      <c r="AGZ57" s="1"/>
+      <c r="AHA57" s="1"/>
+      <c r="AHB57" s="1"/>
+      <c r="AHC57" s="1"/>
+      <c r="AHD57" s="1"/>
+      <c r="AHE57" s="1"/>
+      <c r="AHF57" s="1"/>
+      <c r="AHG57" s="1"/>
+      <c r="AHH57" s="1"/>
+      <c r="AHI57" s="1"/>
+      <c r="AHJ57" s="1"/>
+      <c r="AHK57" s="1"/>
+      <c r="AHL57" s="1"/>
+      <c r="AHM57" s="1"/>
+      <c r="AHN57" s="1"/>
+      <c r="AHO57" s="1"/>
+      <c r="AHP57" s="1"/>
+      <c r="AHQ57" s="1"/>
+      <c r="AHR57" s="1"/>
+      <c r="AHS57" s="1"/>
+      <c r="AHT57" s="1"/>
+      <c r="AHU57" s="1"/>
+      <c r="AHV57" s="1"/>
+      <c r="AHW57" s="1"/>
+      <c r="AHX57" s="1"/>
+      <c r="AHY57" s="1"/>
+      <c r="AHZ57" s="1"/>
+      <c r="AIA57" s="1"/>
+      <c r="AIB57" s="1"/>
+      <c r="AIC57" s="1"/>
+      <c r="AID57" s="1"/>
+      <c r="AIE57" s="1"/>
+      <c r="AIF57" s="1"/>
+      <c r="AIG57" s="1"/>
+      <c r="AIH57" s="1"/>
+      <c r="AII57" s="1"/>
+      <c r="AIJ57" s="1"/>
+      <c r="AIK57" s="1"/>
+      <c r="AIL57" s="1"/>
+      <c r="AIM57" s="1"/>
+      <c r="AIN57" s="1"/>
+      <c r="AIO57" s="1"/>
+      <c r="AIP57" s="1"/>
+      <c r="AIQ57" s="1"/>
+      <c r="AIR57" s="1"/>
+      <c r="AIS57" s="1"/>
+      <c r="AIT57" s="1"/>
+      <c r="AIU57" s="1"/>
+      <c r="AIV57" s="1"/>
+      <c r="AIW57" s="1"/>
+      <c r="AIX57" s="1"/>
+      <c r="AIY57" s="1"/>
+      <c r="AIZ57" s="1"/>
+      <c r="AJA57" s="1"/>
+      <c r="AJB57" s="1"/>
+      <c r="AJC57" s="1"/>
+      <c r="AJD57" s="1"/>
+      <c r="AJE57" s="1"/>
+      <c r="AJF57" s="1"/>
+      <c r="AJG57" s="1"/>
+      <c r="AJH57" s="1"/>
+      <c r="AJI57" s="1"/>
+      <c r="AJJ57" s="1"/>
+      <c r="AJK57" s="1"/>
+      <c r="AJL57" s="1"/>
+      <c r="AJM57" s="1"/>
+      <c r="AJN57" s="1"/>
+      <c r="AJO57" s="1"/>
+      <c r="AJP57" s="1"/>
+      <c r="AJQ57" s="1"/>
+      <c r="AJR57" s="1"/>
+      <c r="AJS57" s="1"/>
+      <c r="AJT57" s="1"/>
+      <c r="AJU57" s="1"/>
+      <c r="AJV57" s="1"/>
+      <c r="AJW57" s="1"/>
+      <c r="AJX57" s="1"/>
+      <c r="AJY57" s="1"/>
+      <c r="AJZ57" s="1"/>
+      <c r="AKA57" s="1"/>
+      <c r="AKB57" s="1"/>
+      <c r="AKC57" s="1"/>
+      <c r="AKD57" s="1"/>
+      <c r="AKE57" s="1"/>
+      <c r="AKF57" s="1"/>
+      <c r="AKG57" s="1"/>
+      <c r="AKH57" s="1"/>
+      <c r="AKI57" s="1"/>
+      <c r="AKJ57" s="1"/>
+      <c r="AKK57" s="1"/>
+      <c r="AKL57" s="1"/>
+      <c r="AKM57" s="1"/>
+      <c r="AKN57" s="1"/>
+      <c r="AKO57" s="1"/>
+      <c r="AKP57" s="1"/>
+      <c r="AKQ57" s="1"/>
+      <c r="AKR57" s="1"/>
+      <c r="AKS57" s="1"/>
+      <c r="AKT57" s="1"/>
+      <c r="AKU57" s="1"/>
+      <c r="AKV57" s="1"/>
+      <c r="AKW57" s="1"/>
+      <c r="AKX57" s="1"/>
+      <c r="AKY57" s="1"/>
+      <c r="AKZ57" s="1"/>
+      <c r="ALA57" s="1"/>
+      <c r="ALB57" s="1"/>
+      <c r="ALC57" s="1"/>
+      <c r="ALD57" s="1"/>
+      <c r="ALE57" s="1"/>
+      <c r="ALF57" s="1"/>
+      <c r="ALG57" s="1"/>
+      <c r="ALH57" s="1"/>
+      <c r="ALI57" s="1"/>
+      <c r="ALJ57" s="1"/>
+      <c r="ALK57" s="1"/>
+      <c r="ALL57" s="1"/>
+      <c r="ALM57" s="1"/>
+      <c r="ALN57" s="1"/>
+      <c r="ALO57" s="1"/>
+      <c r="ALP57" s="1"/>
+      <c r="ALQ57" s="1"/>
+      <c r="ALR57" s="1"/>
+      <c r="ALS57" s="1"/>
+      <c r="ALT57" s="1"/>
+      <c r="ALU57" s="1"/>
+      <c r="ALV57" s="1"/>
+      <c r="ALW57" s="1"/>
+      <c r="ALX57" s="1"/>
+      <c r="ALY57" s="1"/>
+      <c r="ALZ57" s="1"/>
+      <c r="AMA57" s="1"/>
+      <c r="AMB57" s="1"/>
+      <c r="AMC57" s="1"/>
+      <c r="AMD57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
+      <c r="AC58" s="1"/>
+      <c r="AD58" s="1"/>
+      <c r="AE58" s="1"/>
+      <c r="AF58" s="1"/>
+      <c r="AG58" s="1"/>
+      <c r="AH58" s="1"/>
+      <c r="AI58" s="1"/>
+      <c r="AJ58" s="1"/>
+      <c r="AK58" s="1"/>
+      <c r="AL58" s="1"/>
+      <c r="AM58" s="1"/>
+      <c r="AN58" s="1"/>
+      <c r="AO58" s="1"/>
+      <c r="AP58" s="1"/>
+      <c r="AQ58" s="1"/>
+      <c r="AR58" s="1"/>
+      <c r="AS58" s="1"/>
+      <c r="AT58" s="1"/>
+      <c r="AU58" s="1"/>
+      <c r="AV58" s="1"/>
+      <c r="AW58" s="1"/>
+      <c r="AX58" s="1"/>
+      <c r="AY58" s="1"/>
+      <c r="AZ58" s="1"/>
+      <c r="BA58" s="1"/>
+      <c r="BB58" s="1"/>
+      <c r="BC58" s="1"/>
+      <c r="BD58" s="1"/>
+      <c r="BE58" s="1"/>
+      <c r="BF58" s="1"/>
+      <c r="BG58" s="1"/>
+      <c r="BH58" s="1"/>
+      <c r="BI58" s="1"/>
+      <c r="BJ58" s="1"/>
+      <c r="BK58" s="1"/>
+      <c r="BL58" s="1"/>
+      <c r="BM58" s="1"/>
+      <c r="BN58" s="1"/>
+      <c r="BO58" s="1"/>
+      <c r="BP58" s="1"/>
+      <c r="BQ58" s="1"/>
+      <c r="BR58" s="1"/>
+      <c r="BS58" s="1"/>
+      <c r="BT58" s="1"/>
+      <c r="BU58" s="1"/>
+      <c r="BV58" s="1"/>
+      <c r="BW58" s="1"/>
+      <c r="BX58" s="1"/>
+      <c r="BY58" s="1"/>
+      <c r="BZ58" s="1"/>
+      <c r="CA58" s="1"/>
+      <c r="CB58" s="1"/>
+      <c r="CC58" s="1"/>
+      <c r="CD58" s="1"/>
+      <c r="CE58" s="1"/>
+      <c r="CF58" s="1"/>
+      <c r="CG58" s="1"/>
+      <c r="CH58" s="1"/>
+      <c r="CI58" s="1"/>
+      <c r="CJ58" s="1"/>
+      <c r="CK58" s="1"/>
+      <c r="CL58" s="1"/>
+      <c r="CM58" s="1"/>
+      <c r="CN58" s="1"/>
+      <c r="CO58" s="1"/>
+      <c r="CP58" s="1"/>
+      <c r="CQ58" s="1"/>
+      <c r="CR58" s="1"/>
+      <c r="CS58" s="1"/>
+      <c r="CT58" s="1"/>
+      <c r="CU58" s="1"/>
+      <c r="CV58" s="1"/>
+      <c r="CW58" s="1"/>
+      <c r="CX58" s="1"/>
+      <c r="CY58" s="1"/>
+      <c r="CZ58" s="1"/>
+      <c r="DA58" s="1"/>
+      <c r="DB58" s="1"/>
+      <c r="DC58" s="1"/>
+      <c r="DD58" s="1"/>
+      <c r="DE58" s="1"/>
+      <c r="DF58" s="1"/>
+      <c r="DG58" s="1"/>
+      <c r="DH58" s="1"/>
+      <c r="DI58" s="1"/>
+      <c r="DJ58" s="1"/>
+      <c r="DK58" s="1"/>
+      <c r="DL58" s="1"/>
+      <c r="DM58" s="1"/>
+      <c r="DN58" s="1"/>
+      <c r="DO58" s="1"/>
+      <c r="DP58" s="1"/>
+      <c r="DQ58" s="1"/>
+      <c r="DR58" s="1"/>
+      <c r="DS58" s="1"/>
+      <c r="DT58" s="1"/>
+      <c r="DU58" s="1"/>
+      <c r="DV58" s="1"/>
+      <c r="DW58" s="1"/>
+      <c r="DX58" s="1"/>
+      <c r="DY58" s="1"/>
+      <c r="DZ58" s="1"/>
+      <c r="EA58" s="1"/>
+      <c r="EB58" s="1"/>
+      <c r="EC58" s="1"/>
+      <c r="ED58" s="1"/>
+      <c r="EE58" s="1"/>
+      <c r="EF58" s="1"/>
+      <c r="EG58" s="1"/>
+      <c r="EH58" s="1"/>
+      <c r="EI58" s="1"/>
+      <c r="EJ58" s="1"/>
+      <c r="EK58" s="1"/>
+      <c r="EL58" s="1"/>
+      <c r="EM58" s="1"/>
+      <c r="EN58" s="1"/>
+      <c r="EO58" s="1"/>
+      <c r="EP58" s="1"/>
+      <c r="EQ58" s="1"/>
+      <c r="ER58" s="1"/>
+      <c r="ES58" s="1"/>
+      <c r="ET58" s="1"/>
+      <c r="EU58" s="1"/>
+      <c r="EV58" s="1"/>
+      <c r="EW58" s="1"/>
+      <c r="EX58" s="1"/>
+      <c r="EY58" s="1"/>
+      <c r="EZ58" s="1"/>
+      <c r="FA58" s="1"/>
+      <c r="FB58" s="1"/>
+      <c r="FC58" s="1"/>
+      <c r="FD58" s="1"/>
+      <c r="FE58" s="1"/>
+      <c r="FF58" s="1"/>
+      <c r="FG58" s="1"/>
+      <c r="FH58" s="1"/>
+      <c r="FI58" s="1"/>
+      <c r="FJ58" s="1"/>
+      <c r="FK58" s="1"/>
+      <c r="FL58" s="1"/>
+      <c r="FM58" s="1"/>
+      <c r="FN58" s="1"/>
+      <c r="FO58" s="1"/>
+      <c r="FP58" s="1"/>
+      <c r="FQ58" s="1"/>
+      <c r="FR58" s="1"/>
+      <c r="FS58" s="1"/>
+      <c r="FT58" s="1"/>
+      <c r="FU58" s="1"/>
+      <c r="FV58" s="1"/>
+      <c r="FW58" s="1"/>
+      <c r="FX58" s="1"/>
+      <c r="FY58" s="1"/>
+      <c r="FZ58" s="1"/>
+      <c r="GA58" s="1"/>
+      <c r="GB58" s="1"/>
+      <c r="GC58" s="1"/>
+      <c r="GD58" s="1"/>
+      <c r="GE58" s="1"/>
+      <c r="GF58" s="1"/>
+      <c r="GG58" s="1"/>
+      <c r="GH58" s="1"/>
+      <c r="GI58" s="1"/>
+      <c r="GJ58" s="1"/>
+      <c r="GK58" s="1"/>
+      <c r="GL58" s="1"/>
+      <c r="GM58" s="1"/>
+      <c r="GN58" s="1"/>
+      <c r="GO58" s="1"/>
+      <c r="GP58" s="1"/>
+      <c r="GQ58" s="1"/>
+      <c r="GR58" s="1"/>
+      <c r="GS58" s="1"/>
+      <c r="GT58" s="1"/>
+      <c r="GU58" s="1"/>
+      <c r="GV58" s="1"/>
+      <c r="GW58" s="1"/>
+      <c r="GX58" s="1"/>
+      <c r="GY58" s="1"/>
+      <c r="GZ58" s="1"/>
+      <c r="HA58" s="1"/>
+      <c r="HB58" s="1"/>
+      <c r="HC58" s="1"/>
+      <c r="HD58" s="1"/>
+      <c r="HE58" s="1"/>
+      <c r="HF58" s="1"/>
+      <c r="HG58" s="1"/>
+      <c r="HH58" s="1"/>
+      <c r="HI58" s="1"/>
+      <c r="HJ58" s="1"/>
+      <c r="HK58" s="1"/>
+      <c r="HL58" s="1"/>
+      <c r="HM58" s="1"/>
+      <c r="HN58" s="1"/>
+      <c r="HO58" s="1"/>
+      <c r="HP58" s="1"/>
+      <c r="HQ58" s="1"/>
+      <c r="HR58" s="1"/>
+      <c r="HS58" s="1"/>
+      <c r="HT58" s="1"/>
+      <c r="HU58" s="1"/>
+      <c r="HV58" s="1"/>
+      <c r="HW58" s="1"/>
+      <c r="HX58" s="1"/>
+      <c r="HY58" s="1"/>
+      <c r="HZ58" s="1"/>
+      <c r="IA58" s="1"/>
+      <c r="IB58" s="1"/>
+      <c r="IC58" s="1"/>
+      <c r="ID58" s="1"/>
+      <c r="IE58" s="1"/>
+      <c r="IF58" s="1"/>
+      <c r="IG58" s="1"/>
+      <c r="IH58" s="1"/>
+      <c r="II58" s="1"/>
+      <c r="IJ58" s="1"/>
+      <c r="IK58" s="1"/>
+      <c r="IL58" s="1"/>
+      <c r="IM58" s="1"/>
+      <c r="IN58" s="1"/>
+      <c r="IO58" s="1"/>
+      <c r="IP58" s="1"/>
+      <c r="IQ58" s="1"/>
+      <c r="IR58" s="1"/>
+      <c r="IS58" s="1"/>
+      <c r="IT58" s="1"/>
+      <c r="IU58" s="1"/>
+      <c r="IV58" s="1"/>
+      <c r="IW58" s="1"/>
+      <c r="IX58" s="1"/>
+      <c r="IY58" s="1"/>
+      <c r="IZ58" s="1"/>
+      <c r="JA58" s="1"/>
+      <c r="JB58" s="1"/>
+      <c r="JC58" s="1"/>
+      <c r="JD58" s="1"/>
+      <c r="JE58" s="1"/>
+      <c r="JF58" s="1"/>
+      <c r="JG58" s="1"/>
+      <c r="JH58" s="1"/>
+      <c r="JI58" s="1"/>
+      <c r="JJ58" s="1"/>
+      <c r="JK58" s="1"/>
+      <c r="JL58" s="1"/>
+      <c r="JM58" s="1"/>
+      <c r="JN58" s="1"/>
+      <c r="JO58" s="1"/>
+      <c r="JP58" s="1"/>
+      <c r="JQ58" s="1"/>
+      <c r="JR58" s="1"/>
+      <c r="JS58" s="1"/>
+      <c r="JT58" s="1"/>
+      <c r="JU58" s="1"/>
+      <c r="JV58" s="1"/>
+      <c r="JW58" s="1"/>
+      <c r="JX58" s="1"/>
+      <c r="JY58" s="1"/>
+      <c r="JZ58" s="1"/>
+      <c r="KA58" s="1"/>
+      <c r="KB58" s="1"/>
+      <c r="KC58" s="1"/>
+      <c r="KD58" s="1"/>
+      <c r="KE58" s="1"/>
+      <c r="KF58" s="1"/>
+      <c r="KG58" s="1"/>
+      <c r="KH58" s="1"/>
+      <c r="KI58" s="1"/>
+      <c r="KJ58" s="1"/>
+      <c r="KK58" s="1"/>
+      <c r="KL58" s="1"/>
+      <c r="KM58" s="1"/>
+      <c r="KN58" s="1"/>
+      <c r="KO58" s="1"/>
+      <c r="KP58" s="1"/>
+      <c r="KQ58" s="1"/>
+      <c r="KR58" s="1"/>
+      <c r="KS58" s="1"/>
+      <c r="KT58" s="1"/>
+      <c r="KU58" s="1"/>
+      <c r="KV58" s="1"/>
+      <c r="KW58" s="1"/>
+      <c r="KX58" s="1"/>
+      <c r="KY58" s="1"/>
+      <c r="KZ58" s="1"/>
+      <c r="LA58" s="1"/>
+      <c r="LB58" s="1"/>
+      <c r="LC58" s="1"/>
+      <c r="LD58" s="1"/>
+      <c r="LE58" s="1"/>
+      <c r="LF58" s="1"/>
+      <c r="LG58" s="1"/>
+      <c r="LH58" s="1"/>
+      <c r="LI58" s="1"/>
+      <c r="LJ58" s="1"/>
+      <c r="LK58" s="1"/>
+      <c r="LL58" s="1"/>
+      <c r="LM58" s="1"/>
+      <c r="LN58" s="1"/>
+      <c r="LO58" s="1"/>
+      <c r="LP58" s="1"/>
+      <c r="LQ58" s="1"/>
+      <c r="LR58" s="1"/>
+      <c r="LS58" s="1"/>
+      <c r="LT58" s="1"/>
+      <c r="LU58" s="1"/>
+      <c r="LV58" s="1"/>
+      <c r="LW58" s="1"/>
+      <c r="LX58" s="1"/>
+      <c r="LY58" s="1"/>
+      <c r="LZ58" s="1"/>
+      <c r="MA58" s="1"/>
+      <c r="MB58" s="1"/>
+      <c r="MC58" s="1"/>
+      <c r="MD58" s="1"/>
+      <c r="ME58" s="1"/>
+      <c r="MF58" s="1"/>
+      <c r="MG58" s="1"/>
+      <c r="MH58" s="1"/>
+      <c r="MI58" s="1"/>
+      <c r="MJ58" s="1"/>
+      <c r="MK58" s="1"/>
+      <c r="ML58" s="1"/>
+      <c r="MM58" s="1"/>
+      <c r="MN58" s="1"/>
+      <c r="MO58" s="1"/>
+      <c r="MP58" s="1"/>
+      <c r="MQ58" s="1"/>
+      <c r="MR58" s="1"/>
+      <c r="MS58" s="1"/>
+      <c r="MT58" s="1"/>
+      <c r="MU58" s="1"/>
+      <c r="MV58" s="1"/>
+      <c r="MW58" s="1"/>
+      <c r="MX58" s="1"/>
+      <c r="MY58" s="1"/>
+      <c r="MZ58" s="1"/>
+      <c r="NA58" s="1"/>
+      <c r="NB58" s="1"/>
+      <c r="NC58" s="1"/>
+      <c r="ND58" s="1"/>
+      <c r="NE58" s="1"/>
+      <c r="NF58" s="1"/>
+      <c r="NG58" s="1"/>
+      <c r="NH58" s="1"/>
+      <c r="NI58" s="1"/>
+      <c r="NJ58" s="1"/>
+      <c r="NK58" s="1"/>
+      <c r="NL58" s="1"/>
+      <c r="NM58" s="1"/>
+      <c r="NN58" s="1"/>
+      <c r="NO58" s="1"/>
+      <c r="NP58" s="1"/>
+      <c r="NQ58" s="1"/>
+      <c r="NR58" s="1"/>
+      <c r="NS58" s="1"/>
+      <c r="NT58" s="1"/>
+      <c r="NU58" s="1"/>
+      <c r="NV58" s="1"/>
+      <c r="NW58" s="1"/>
+      <c r="NX58" s="1"/>
+      <c r="NY58" s="1"/>
+      <c r="NZ58" s="1"/>
+      <c r="OA58" s="1"/>
+      <c r="OB58" s="1"/>
+      <c r="OC58" s="1"/>
+      <c r="OD58" s="1"/>
+      <c r="OE58" s="1"/>
+      <c r="OF58" s="1"/>
+      <c r="OG58" s="1"/>
+      <c r="OH58" s="1"/>
+      <c r="OI58" s="1"/>
+      <c r="OJ58" s="1"/>
+      <c r="OK58" s="1"/>
+      <c r="OL58" s="1"/>
+      <c r="OM58" s="1"/>
+      <c r="ON58" s="1"/>
+      <c r="OO58" s="1"/>
+      <c r="OP58" s="1"/>
+      <c r="OQ58" s="1"/>
+      <c r="OR58" s="1"/>
+      <c r="OS58" s="1"/>
+      <c r="OT58" s="1"/>
+      <c r="OU58" s="1"/>
+      <c r="OV58" s="1"/>
+      <c r="OW58" s="1"/>
+      <c r="OX58" s="1"/>
+      <c r="OY58" s="1"/>
+      <c r="OZ58" s="1"/>
+      <c r="PA58" s="1"/>
+      <c r="PB58" s="1"/>
+      <c r="PC58" s="1"/>
+      <c r="PD58" s="1"/>
+      <c r="PE58" s="1"/>
+      <c r="PF58" s="1"/>
+      <c r="PG58" s="1"/>
+      <c r="PH58" s="1"/>
+      <c r="PI58" s="1"/>
+      <c r="PJ58" s="1"/>
+      <c r="PK58" s="1"/>
+      <c r="PL58" s="1"/>
+      <c r="PM58" s="1"/>
+      <c r="PN58" s="1"/>
+      <c r="PO58" s="1"/>
+      <c r="PP58" s="1"/>
+      <c r="PQ58" s="1"/>
+      <c r="PR58" s="1"/>
+      <c r="PS58" s="1"/>
+      <c r="PT58" s="1"/>
+      <c r="PU58" s="1"/>
+      <c r="PV58" s="1"/>
+      <c r="PW58" s="1"/>
+      <c r="PX58" s="1"/>
+      <c r="PY58" s="1"/>
+      <c r="PZ58" s="1"/>
+      <c r="QA58" s="1"/>
+      <c r="QB58" s="1"/>
+      <c r="QC58" s="1"/>
+      <c r="QD58" s="1"/>
+      <c r="QE58" s="1"/>
+      <c r="QF58" s="1"/>
+      <c r="QG58" s="1"/>
+      <c r="QH58" s="1"/>
+      <c r="QI58" s="1"/>
+      <c r="QJ58" s="1"/>
+      <c r="QK58" s="1"/>
+      <c r="QL58" s="1"/>
+      <c r="QM58" s="1"/>
+      <c r="QN58" s="1"/>
+      <c r="QO58" s="1"/>
+      <c r="QP58" s="1"/>
+      <c r="QQ58" s="1"/>
+      <c r="QR58" s="1"/>
+      <c r="QS58" s="1"/>
+      <c r="QT58" s="1"/>
+      <c r="QU58" s="1"/>
+      <c r="QV58" s="1"/>
+      <c r="QW58" s="1"/>
+      <c r="QX58" s="1"/>
+      <c r="QY58" s="1"/>
+      <c r="QZ58" s="1"/>
+      <c r="RA58" s="1"/>
+      <c r="RB58" s="1"/>
+      <c r="RC58" s="1"/>
+      <c r="RD58" s="1"/>
+      <c r="RE58" s="1"/>
+      <c r="RF58" s="1"/>
+      <c r="RG58" s="1"/>
+      <c r="RH58" s="1"/>
+      <c r="RI58" s="1"/>
+      <c r="RJ58" s="1"/>
+      <c r="RK58" s="1"/>
+      <c r="RL58" s="1"/>
+      <c r="RM58" s="1"/>
+      <c r="RN58" s="1"/>
+      <c r="RO58" s="1"/>
+      <c r="RP58" s="1"/>
+      <c r="RQ58" s="1"/>
+      <c r="RR58" s="1"/>
+      <c r="RS58" s="1"/>
+      <c r="RT58" s="1"/>
+      <c r="RU58" s="1"/>
+      <c r="RV58" s="1"/>
+      <c r="RW58" s="1"/>
+      <c r="RX58" s="1"/>
+      <c r="RY58" s="1"/>
+      <c r="RZ58" s="1"/>
+      <c r="SA58" s="1"/>
+      <c r="SB58" s="1"/>
+      <c r="SC58" s="1"/>
+      <c r="SD58" s="1"/>
+      <c r="SE58" s="1"/>
+      <c r="SF58" s="1"/>
+      <c r="SG58" s="1"/>
+      <c r="SH58" s="1"/>
+      <c r="SI58" s="1"/>
+      <c r="SJ58" s="1"/>
+      <c r="SK58" s="1"/>
+      <c r="SL58" s="1"/>
+      <c r="SM58" s="1"/>
+      <c r="SN58" s="1"/>
+      <c r="SO58" s="1"/>
+      <c r="SP58" s="1"/>
+      <c r="SQ58" s="1"/>
+      <c r="SR58" s="1"/>
+      <c r="SS58" s="1"/>
+      <c r="ST58" s="1"/>
+      <c r="SU58" s="1"/>
+      <c r="SV58" s="1"/>
+      <c r="SW58" s="1"/>
+      <c r="SX58" s="1"/>
+      <c r="SY58" s="1"/>
+      <c r="SZ58" s="1"/>
+      <c r="TA58" s="1"/>
+      <c r="TB58" s="1"/>
+      <c r="TC58" s="1"/>
+      <c r="TD58" s="1"/>
+      <c r="TE58" s="1"/>
+      <c r="TF58" s="1"/>
+      <c r="TG58" s="1"/>
+      <c r="TH58" s="1"/>
+      <c r="TI58" s="1"/>
+      <c r="TJ58" s="1"/>
+      <c r="TK58" s="1"/>
+      <c r="TL58" s="1"/>
+      <c r="TM58" s="1"/>
+      <c r="TN58" s="1"/>
+      <c r="TO58" s="1"/>
+      <c r="TP58" s="1"/>
+      <c r="TQ58" s="1"/>
+      <c r="TR58" s="1"/>
+      <c r="TS58" s="1"/>
+      <c r="TT58" s="1"/>
+      <c r="TU58" s="1"/>
+      <c r="TV58" s="1"/>
+      <c r="TW58" s="1"/>
+      <c r="TX58" s="1"/>
+      <c r="TY58" s="1"/>
+      <c r="TZ58" s="1"/>
+      <c r="UA58" s="1"/>
+      <c r="UB58" s="1"/>
+      <c r="UC58" s="1"/>
+      <c r="UD58" s="1"/>
+      <c r="UE58" s="1"/>
+      <c r="UF58" s="1"/>
+      <c r="UG58" s="1"/>
+      <c r="UH58" s="1"/>
+      <c r="UI58" s="1"/>
+      <c r="UJ58" s="1"/>
+      <c r="UK58" s="1"/>
+      <c r="UL58" s="1"/>
+      <c r="UM58" s="1"/>
+      <c r="UN58" s="1"/>
+      <c r="UO58" s="1"/>
+      <c r="UP58" s="1"/>
+      <c r="UQ58" s="1"/>
+      <c r="UR58" s="1"/>
+      <c r="US58" s="1"/>
+      <c r="UT58" s="1"/>
+      <c r="UU58" s="1"/>
+      <c r="UV58" s="1"/>
+      <c r="UW58" s="1"/>
+      <c r="UX58" s="1"/>
+      <c r="UY58" s="1"/>
+      <c r="UZ58" s="1"/>
+      <c r="VA58" s="1"/>
+      <c r="VB58" s="1"/>
+      <c r="VC58" s="1"/>
+      <c r="VD58" s="1"/>
+      <c r="VE58" s="1"/>
+      <c r="VF58" s="1"/>
+      <c r="VG58" s="1"/>
+      <c r="VH58" s="1"/>
+      <c r="VI58" s="1"/>
+      <c r="VJ58" s="1"/>
+      <c r="VK58" s="1"/>
+      <c r="VL58" s="1"/>
+      <c r="VM58" s="1"/>
+      <c r="VN58" s="1"/>
+      <c r="VO58" s="1"/>
+      <c r="VP58" s="1"/>
+      <c r="VQ58" s="1"/>
+      <c r="VR58" s="1"/>
+      <c r="VS58" s="1"/>
+      <c r="VT58" s="1"/>
+      <c r="VU58" s="1"/>
+      <c r="VV58" s="1"/>
+      <c r="VW58" s="1"/>
+      <c r="VX58" s="1"/>
+      <c r="VY58" s="1"/>
+      <c r="VZ58" s="1"/>
+      <c r="WA58" s="1"/>
+      <c r="WB58" s="1"/>
+      <c r="WC58" s="1"/>
+      <c r="WD58" s="1"/>
+      <c r="WE58" s="1"/>
+      <c r="WF58" s="1"/>
+      <c r="WG58" s="1"/>
+      <c r="WH58" s="1"/>
+      <c r="WI58" s="1"/>
+      <c r="WJ58" s="1"/>
+      <c r="WK58" s="1"/>
+      <c r="WL58" s="1"/>
+      <c r="WM58" s="1"/>
+      <c r="WN58" s="1"/>
+      <c r="WO58" s="1"/>
+      <c r="WP58" s="1"/>
+      <c r="WQ58" s="1"/>
+      <c r="WR58" s="1"/>
+      <c r="WS58" s="1"/>
+      <c r="WT58" s="1"/>
+      <c r="WU58" s="1"/>
+      <c r="WV58" s="1"/>
+      <c r="WW58" s="1"/>
+      <c r="WX58" s="1"/>
+      <c r="WY58" s="1"/>
+      <c r="WZ58" s="1"/>
+      <c r="XA58" s="1"/>
+      <c r="XB58" s="1"/>
+      <c r="XC58" s="1"/>
+      <c r="XD58" s="1"/>
+      <c r="XE58" s="1"/>
+      <c r="XF58" s="1"/>
+      <c r="XG58" s="1"/>
+      <c r="XH58" s="1"/>
+      <c r="XI58" s="1"/>
+      <c r="XJ58" s="1"/>
+      <c r="XK58" s="1"/>
+      <c r="XL58" s="1"/>
+      <c r="XM58" s="1"/>
+      <c r="XN58" s="1"/>
+      <c r="XO58" s="1"/>
+      <c r="XP58" s="1"/>
+      <c r="XQ58" s="1"/>
+      <c r="XR58" s="1"/>
+      <c r="XS58" s="1"/>
+      <c r="XT58" s="1"/>
+      <c r="XU58" s="1"/>
+      <c r="XV58" s="1"/>
+      <c r="XW58" s="1"/>
+      <c r="XX58" s="1"/>
+      <c r="XY58" s="1"/>
+      <c r="XZ58" s="1"/>
+      <c r="YA58" s="1"/>
+      <c r="YB58" s="1"/>
+      <c r="YC58" s="1"/>
+      <c r="YD58" s="1"/>
+      <c r="YE58" s="1"/>
+      <c r="YF58" s="1"/>
+      <c r="YG58" s="1"/>
+      <c r="YH58" s="1"/>
+      <c r="YI58" s="1"/>
+      <c r="YJ58" s="1"/>
+      <c r="YK58" s="1"/>
+      <c r="YL58" s="1"/>
+      <c r="YM58" s="1"/>
+      <c r="YN58" s="1"/>
+      <c r="YO58" s="1"/>
+      <c r="YP58" s="1"/>
+      <c r="YQ58" s="1"/>
+      <c r="YR58" s="1"/>
+      <c r="YS58" s="1"/>
+      <c r="YT58" s="1"/>
+      <c r="YU58" s="1"/>
+      <c r="YV58" s="1"/>
+      <c r="YW58" s="1"/>
+      <c r="YX58" s="1"/>
+      <c r="YY58" s="1"/>
+      <c r="YZ58" s="1"/>
+      <c r="ZA58" s="1"/>
+      <c r="ZB58" s="1"/>
+      <c r="ZC58" s="1"/>
+      <c r="ZD58" s="1"/>
+      <c r="ZE58" s="1"/>
+      <c r="ZF58" s="1"/>
+      <c r="ZG58" s="1"/>
+      <c r="ZH58" s="1"/>
+      <c r="ZI58" s="1"/>
+      <c r="ZJ58" s="1"/>
+      <c r="ZK58" s="1"/>
+      <c r="ZL58" s="1"/>
+      <c r="ZM58" s="1"/>
+      <c r="ZN58" s="1"/>
+      <c r="ZO58" s="1"/>
+      <c r="ZP58" s="1"/>
+      <c r="ZQ58" s="1"/>
+      <c r="ZR58" s="1"/>
+      <c r="ZS58" s="1"/>
+      <c r="ZT58" s="1"/>
+      <c r="ZU58" s="1"/>
+      <c r="ZV58" s="1"/>
+      <c r="ZW58" s="1"/>
+      <c r="ZX58" s="1"/>
+      <c r="ZY58" s="1"/>
+      <c r="ZZ58" s="1"/>
+      <c r="AAA58" s="1"/>
+      <c r="AAB58" s="1"/>
+      <c r="AAC58" s="1"/>
+      <c r="AAD58" s="1"/>
+      <c r="AAE58" s="1"/>
+      <c r="AAF58" s="1"/>
+      <c r="AAG58" s="1"/>
+      <c r="AAH58" s="1"/>
+      <c r="AAI58" s="1"/>
+      <c r="AAJ58" s="1"/>
+      <c r="AAK58" s="1"/>
+      <c r="AAL58" s="1"/>
+      <c r="AAM58" s="1"/>
+      <c r="AAN58" s="1"/>
+      <c r="AAO58" s="1"/>
+      <c r="AAP58" s="1"/>
+      <c r="AAQ58" s="1"/>
+      <c r="AAR58" s="1"/>
+      <c r="AAS58" s="1"/>
+      <c r="AAT58" s="1"/>
+      <c r="AAU58" s="1"/>
+      <c r="AAV58" s="1"/>
+      <c r="AAW58" s="1"/>
+      <c r="AAX58" s="1"/>
+      <c r="AAY58" s="1"/>
+      <c r="AAZ58" s="1"/>
+      <c r="ABA58" s="1"/>
+      <c r="ABB58" s="1"/>
+      <c r="ABC58" s="1"/>
+      <c r="ABD58" s="1"/>
+      <c r="ABE58" s="1"/>
+      <c r="ABF58" s="1"/>
+      <c r="ABG58" s="1"/>
+      <c r="ABH58" s="1"/>
+      <c r="ABI58" s="1"/>
+      <c r="ABJ58" s="1"/>
+      <c r="ABK58" s="1"/>
+      <c r="ABL58" s="1"/>
+      <c r="ABM58" s="1"/>
+      <c r="ABN58" s="1"/>
+      <c r="ABO58" s="1"/>
+      <c r="ABP58" s="1"/>
+      <c r="ABQ58" s="1"/>
+      <c r="ABR58" s="1"/>
+      <c r="ABS58" s="1"/>
+      <c r="ABT58" s="1"/>
+      <c r="ABU58" s="1"/>
+      <c r="ABV58" s="1"/>
+      <c r="ABW58" s="1"/>
+      <c r="ABX58" s="1"/>
+      <c r="ABY58" s="1"/>
+      <c r="ABZ58" s="1"/>
+      <c r="ACA58" s="1"/>
+      <c r="ACB58" s="1"/>
+      <c r="ACC58" s="1"/>
+      <c r="ACD58" s="1"/>
+      <c r="ACE58" s="1"/>
+      <c r="ACF58" s="1"/>
+      <c r="ACG58" s="1"/>
+      <c r="ACH58" s="1"/>
+      <c r="ACI58" s="1"/>
+      <c r="ACJ58" s="1"/>
+      <c r="ACK58" s="1"/>
+      <c r="ACL58" s="1"/>
+      <c r="ACM58" s="1"/>
+      <c r="ACN58" s="1"/>
+      <c r="ACO58" s="1"/>
+      <c r="ACP58" s="1"/>
+      <c r="ACQ58" s="1"/>
+      <c r="ACR58" s="1"/>
+      <c r="ACS58" s="1"/>
+      <c r="ACT58" s="1"/>
+      <c r="ACU58" s="1"/>
+      <c r="ACV58" s="1"/>
+      <c r="ACW58" s="1"/>
+      <c r="ACX58" s="1"/>
+      <c r="ACY58" s="1"/>
+      <c r="ACZ58" s="1"/>
+      <c r="ADA58" s="1"/>
+      <c r="ADB58" s="1"/>
+      <c r="ADC58" s="1"/>
+      <c r="ADD58" s="1"/>
+      <c r="ADE58" s="1"/>
+      <c r="ADF58" s="1"/>
+      <c r="ADG58" s="1"/>
+      <c r="ADH58" s="1"/>
+      <c r="ADI58" s="1"/>
+      <c r="ADJ58" s="1"/>
+      <c r="ADK58" s="1"/>
+      <c r="ADL58" s="1"/>
+      <c r="ADM58" s="1"/>
+      <c r="ADN58" s="1"/>
+      <c r="ADO58" s="1"/>
+      <c r="ADP58" s="1"/>
+      <c r="ADQ58" s="1"/>
+      <c r="ADR58" s="1"/>
+      <c r="ADS58" s="1"/>
+      <c r="ADT58" s="1"/>
+      <c r="ADU58" s="1"/>
+      <c r="ADV58" s="1"/>
+      <c r="ADW58" s="1"/>
+      <c r="ADX58" s="1"/>
+      <c r="ADY58" s="1"/>
+      <c r="ADZ58" s="1"/>
+      <c r="AEA58" s="1"/>
+      <c r="AEB58" s="1"/>
+      <c r="AEC58" s="1"/>
+      <c r="AED58" s="1"/>
+      <c r="AEE58" s="1"/>
+      <c r="AEF58" s="1"/>
+      <c r="AEG58" s="1"/>
+      <c r="AEH58" s="1"/>
+      <c r="AEI58" s="1"/>
+      <c r="AEJ58" s="1"/>
+      <c r="AEK58" s="1"/>
+      <c r="AEL58" s="1"/>
+      <c r="AEM58" s="1"/>
+      <c r="AEN58" s="1"/>
+      <c r="AEO58" s="1"/>
+      <c r="AEP58" s="1"/>
+      <c r="AEQ58" s="1"/>
+      <c r="AER58" s="1"/>
+      <c r="AES58" s="1"/>
+      <c r="AET58" s="1"/>
+      <c r="AEU58" s="1"/>
+      <c r="AEV58" s="1"/>
+      <c r="AEW58" s="1"/>
+      <c r="AEX58" s="1"/>
+      <c r="AEY58" s="1"/>
+      <c r="AEZ58" s="1"/>
+      <c r="AFA58" s="1"/>
+      <c r="AFB58" s="1"/>
+      <c r="AFC58" s="1"/>
+      <c r="AFD58" s="1"/>
+      <c r="AFE58" s="1"/>
+      <c r="AFF58" s="1"/>
+      <c r="AFG58" s="1"/>
+      <c r="AFH58" s="1"/>
+      <c r="AFI58" s="1"/>
+      <c r="AFJ58" s="1"/>
+      <c r="AFK58" s="1"/>
+      <c r="AFL58" s="1"/>
+      <c r="AFM58" s="1"/>
+      <c r="AFN58" s="1"/>
+      <c r="AFO58" s="1"/>
+      <c r="AFP58" s="1"/>
+      <c r="AFQ58" s="1"/>
+      <c r="AFR58" s="1"/>
+      <c r="AFS58" s="1"/>
+      <c r="AFT58" s="1"/>
+      <c r="AFU58" s="1"/>
+      <c r="AFV58" s="1"/>
+      <c r="AFW58" s="1"/>
+      <c r="AFX58" s="1"/>
+      <c r="AFY58" s="1"/>
+      <c r="AFZ58" s="1"/>
+      <c r="AGA58" s="1"/>
+      <c r="AGB58" s="1"/>
+      <c r="AGC58" s="1"/>
+      <c r="AGD58" s="1"/>
+      <c r="AGE58" s="1"/>
+      <c r="AGF58" s="1"/>
+      <c r="AGG58" s="1"/>
+      <c r="AGH58" s="1"/>
+      <c r="AGI58" s="1"/>
+      <c r="AGJ58" s="1"/>
+      <c r="AGK58" s="1"/>
+      <c r="AGL58" s="1"/>
+      <c r="AGM58" s="1"/>
+      <c r="AGN58" s="1"/>
+      <c r="AGO58" s="1"/>
+      <c r="AGP58" s="1"/>
+      <c r="AGQ58" s="1"/>
+      <c r="AGR58" s="1"/>
+      <c r="AGS58" s="1"/>
+      <c r="AGT58" s="1"/>
+      <c r="AGU58" s="1"/>
+      <c r="AGV58" s="1"/>
+      <c r="AGW58" s="1"/>
+      <c r="AGX58" s="1"/>
+      <c r="AGY58" s="1"/>
+      <c r="AGZ58" s="1"/>
+      <c r="AHA58" s="1"/>
+      <c r="AHB58" s="1"/>
+      <c r="AHC58" s="1"/>
+      <c r="AHD58" s="1"/>
+      <c r="AHE58" s="1"/>
+      <c r="AHF58" s="1"/>
+      <c r="AHG58" s="1"/>
+      <c r="AHH58" s="1"/>
+      <c r="AHI58" s="1"/>
+      <c r="AHJ58" s="1"/>
+      <c r="AHK58" s="1"/>
+      <c r="AHL58" s="1"/>
+      <c r="AHM58" s="1"/>
+      <c r="AHN58" s="1"/>
+      <c r="AHO58" s="1"/>
+      <c r="AHP58" s="1"/>
+      <c r="AHQ58" s="1"/>
+      <c r="AHR58" s="1"/>
+      <c r="AHS58" s="1"/>
+      <c r="AHT58" s="1"/>
+      <c r="AHU58" s="1"/>
+      <c r="AHV58" s="1"/>
+      <c r="AHW58" s="1"/>
+      <c r="AHX58" s="1"/>
+      <c r="AHY58" s="1"/>
+      <c r="AHZ58" s="1"/>
+      <c r="AIA58" s="1"/>
+      <c r="AIB58" s="1"/>
+      <c r="AIC58" s="1"/>
+      <c r="AID58" s="1"/>
+      <c r="AIE58" s="1"/>
+      <c r="AIF58" s="1"/>
+      <c r="AIG58" s="1"/>
+      <c r="AIH58" s="1"/>
+      <c r="AII58" s="1"/>
+      <c r="AIJ58" s="1"/>
+      <c r="AIK58" s="1"/>
+      <c r="AIL58" s="1"/>
+      <c r="AIM58" s="1"/>
+      <c r="AIN58" s="1"/>
+      <c r="AIO58" s="1"/>
+      <c r="AIP58" s="1"/>
+      <c r="AIQ58" s="1"/>
+      <c r="AIR58" s="1"/>
+      <c r="AIS58" s="1"/>
+      <c r="AIT58" s="1"/>
+      <c r="AIU58" s="1"/>
+      <c r="AIV58" s="1"/>
+      <c r="AIW58" s="1"/>
+      <c r="AIX58" s="1"/>
+      <c r="AIY58" s="1"/>
+      <c r="AIZ58" s="1"/>
+      <c r="AJA58" s="1"/>
+      <c r="AJB58" s="1"/>
+      <c r="AJC58" s="1"/>
+      <c r="AJD58" s="1"/>
+      <c r="AJE58" s="1"/>
+      <c r="AJF58" s="1"/>
+      <c r="AJG58" s="1"/>
+      <c r="AJH58" s="1"/>
+      <c r="AJI58" s="1"/>
+      <c r="AJJ58" s="1"/>
+      <c r="AJK58" s="1"/>
+      <c r="AJL58" s="1"/>
+      <c r="AJM58" s="1"/>
+      <c r="AJN58" s="1"/>
+      <c r="AJO58" s="1"/>
+      <c r="AJP58" s="1"/>
+      <c r="AJQ58" s="1"/>
+      <c r="AJR58" s="1"/>
+      <c r="AJS58" s="1"/>
+      <c r="AJT58" s="1"/>
+      <c r="AJU58" s="1"/>
+      <c r="AJV58" s="1"/>
+      <c r="AJW58" s="1"/>
+      <c r="AJX58" s="1"/>
+      <c r="AJY58" s="1"/>
+      <c r="AJZ58" s="1"/>
+      <c r="AKA58" s="1"/>
+      <c r="AKB58" s="1"/>
+      <c r="AKC58" s="1"/>
+      <c r="AKD58" s="1"/>
+      <c r="AKE58" s="1"/>
+      <c r="AKF58" s="1"/>
+      <c r="AKG58" s="1"/>
+      <c r="AKH58" s="1"/>
+      <c r="AKI58" s="1"/>
+      <c r="AKJ58" s="1"/>
+      <c r="AKK58" s="1"/>
+      <c r="AKL58" s="1"/>
+      <c r="AKM58" s="1"/>
+      <c r="AKN58" s="1"/>
+      <c r="AKO58" s="1"/>
+      <c r="AKP58" s="1"/>
+      <c r="AKQ58" s="1"/>
+      <c r="AKR58" s="1"/>
+      <c r="AKS58" s="1"/>
+      <c r="AKT58" s="1"/>
+      <c r="AKU58" s="1"/>
+      <c r="AKV58" s="1"/>
+      <c r="AKW58" s="1"/>
+      <c r="AKX58" s="1"/>
+      <c r="AKY58" s="1"/>
+      <c r="AKZ58" s="1"/>
+      <c r="ALA58" s="1"/>
+      <c r="ALB58" s="1"/>
+      <c r="ALC58" s="1"/>
+      <c r="ALD58" s="1"/>
+      <c r="ALE58" s="1"/>
+      <c r="ALF58" s="1"/>
+      <c r="ALG58" s="1"/>
+      <c r="ALH58" s="1"/>
+      <c r="ALI58" s="1"/>
+      <c r="ALJ58" s="1"/>
+      <c r="ALK58" s="1"/>
+      <c r="ALL58" s="1"/>
+      <c r="ALM58" s="1"/>
+      <c r="ALN58" s="1"/>
+      <c r="ALO58" s="1"/>
+      <c r="ALP58" s="1"/>
+      <c r="ALQ58" s="1"/>
+      <c r="ALR58" s="1"/>
+      <c r="ALS58" s="1"/>
+      <c r="ALT58" s="1"/>
+      <c r="ALU58" s="1"/>
+      <c r="ALV58" s="1"/>
+      <c r="ALW58" s="1"/>
+      <c r="ALX58" s="1"/>
+      <c r="ALY58" s="1"/>
+      <c r="ALZ58" s="1"/>
+      <c r="AMA58" s="1"/>
+      <c r="AMB58" s="1"/>
+      <c r="AMC58" s="1"/>
+      <c r="AMD58" s="1"/>
+    </row>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.15138888888889" bottom="1.15138888888889" header="0.7875" footer="0.7875"/>
